--- a/results/DR_results/02_taxa_assemblage/Wards_LDA/cluster_classifier/tables/mccv_classification_report.xlsx
+++ b/results/DR_results/02_taxa_assemblage/Wards_LDA/cluster_classifier/tables/mccv_classification_report.xlsx
@@ -458,17 +458,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>0.645 ± 0.303</t>
+          <t>0.692 ± 0.346</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>0.688 ± 0.320</t>
+          <t>0.637 ± 0.332</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.636 ± 0.266</t>
+          <t>0.630 ± 0.292</t>
         </is>
       </c>
       <c r="E2" t="n">
@@ -483,17 +483,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>0.734 ± 0.169</t>
+          <t>0.843 ± 0.139</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>0.735 ± 0.207</t>
+          <t>0.850 ± 0.188</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>0.716 ± 0.155</t>
+          <t>0.831 ± 0.135</t>
         </is>
       </c>
       <c r="E3" t="n">
@@ -508,21 +508,21 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>0.373 ± 0.444</t>
+          <t>0.000 ± 0.000</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>0.449 ± 0.497</t>
+          <t>0.000 ± 0.000</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>0.398 ± 0.454</t>
+          <t>0.000 ± 0.000</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -540,21 +540,21 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>0.657 ± 0.190</t>
+          <t>0.793 ± 0.185</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>0.680 ± 0.156</t>
+          <t>0.779 ± 0.160</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>0.648 ± 0.169</t>
+          <t>0.764 ± 0.172</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="7">
@@ -574,7 +574,7 @@
       <c r="C8" t="inlineStr"/>
       <c r="D8" t="inlineStr">
         <is>
-          <t>0.680 ± 0.156</t>
+          <t>0.779 ± 0.160</t>
         </is>
       </c>
       <c r="E8" t="inlineStr"/>
@@ -589,7 +589,7 @@
       <c r="C9" t="inlineStr"/>
       <c r="D9" t="inlineStr">
         <is>
-          <t>0.7143</t>
+          <t>0.8333</t>
         </is>
       </c>
       <c r="E9" t="inlineStr"/>
